--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run9/epoch_100/per_file_predictions_epoch_100.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run9/epoch_100/per_file_predictions_epoch_100.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="487">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="488">
   <si>
     <t>Filename</t>
   </si>
@@ -808,673 +808,676 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0,1,0,1</t>
-  </si>
-  <si>
-    <t>0.9218,0.0020,0.0693,0.0004</t>
-  </si>
-  <si>
-    <t>0.0012,0.0001,0.0001,0.9996</t>
-  </si>
-  <si>
-    <t>0.9896,0.0002,0.0003,0.0058</t>
-  </si>
-  <si>
-    <t>0.1183,0.0003,0.0000,0.9653</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0.9945,0.0014,0.0014,0.0003</t>
+  </si>
+  <si>
+    <t>0.0013,0.0001,0.0000,0.9996</t>
+  </si>
+  <si>
+    <t>0.9744,0.0002,0.0010,0.0128</t>
+  </si>
+  <si>
+    <t>0.8956,0.0001,0.0001,0.1191</t>
   </si>
   <si>
     <t>1.0000,0.0000,0.0000,0.0000</t>
   </si>
   <si>
+    <t>0.9993,0.0004,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9999,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9983,0.0013,0.0001,0.0001</t>
+  </si>
+  <si>
     <t>0.9999,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9995,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9985,0.0014,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0004,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9593,0.0003,0.0396,0.0003</t>
-  </si>
-  <si>
-    <t>0.0020,0.0011,0.9978,0.0001</t>
-  </si>
-  <si>
-    <t>0.0153,0.0017,0.9895,0.0000</t>
-  </si>
-  <si>
-    <t>0.2157,0.0001,0.8781,0.0001</t>
-  </si>
-  <si>
-    <t>0.9713,0.0026,0.0190,0.0005</t>
+    <t>0.8980,0.0010,0.0896,0.0008</t>
+  </si>
+  <si>
+    <t>0.0004,0.0003,0.9995,0.0001</t>
+  </si>
+  <si>
+    <t>0.2064,0.0001,0.9461,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.9986,0.0003,0.0003,0.0000</t>
   </si>
   <si>
     <t>0.0000,1.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.0008,0.9985,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.0483,0.9684,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.7510,0.0003,0.3010,0.0004</t>
-  </si>
-  <si>
-    <t>0.0012,0.0003,0.9982,0.0001</t>
+    <t>0.0014,0.9979,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.0312,0.9764,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.9993,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.5716,0.0026,0.0377,0.1405</t>
+  </si>
+  <si>
+    <t>0.0146,0.0025,0.9783,0.0009</t>
+  </si>
+  <si>
+    <t>0.0056,0.0001,0.9969,0.0000</t>
+  </si>
+  <si>
+    <t>0.0626,0.0016,0.9050,0.0003</t>
+  </si>
+  <si>
+    <t>0.0085,0.0003,0.9944,0.0001</t>
+  </si>
+  <si>
+    <t>0.0479,0.0000,0.9795,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.0000,0.9986,0.0001</t>
+  </si>
+  <si>
+    <t>0.0285,0.9672,0.0023,0.0017</t>
+  </si>
+  <si>
+    <t>0.3919,0.0084,0.5646,0.0035</t>
+  </si>
+  <si>
+    <t>0.0007,0.0042,0.9987,0.0077</t>
+  </si>
+  <si>
+    <t>0.0024,0.9085,0.4129,0.0005</t>
+  </si>
+  <si>
+    <t>0.9341,0.0337,0.0107,0.0035</t>
+  </si>
+  <si>
+    <t>0.9959,0.0019,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.8495,0.1784,0.0024,0.0001</t>
+  </si>
+  <si>
+    <t>0.0020,0.9920,0.0220,0.0002</t>
+  </si>
+  <si>
+    <t>0.0053,0.0239,0.9402,0.0059</t>
+  </si>
+  <si>
+    <t>0.0015,0.0008,0.9942,0.0035</t>
+  </si>
+  <si>
+    <t>0.0133,0.0018,0.9738,0.0011</t>
+  </si>
+  <si>
+    <t>0.0008,0.0000,0.9988,0.0001</t>
+  </si>
+  <si>
+    <t>0.0006,0.0051,0.9984,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.9989,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.0004,0.0003,0.9988,0.0005</t>
+  </si>
+  <si>
+    <t>0.0057,0.1194,0.0058,0.9775</t>
+  </si>
+  <si>
+    <t>0.0048,0.9894,0.0026,0.0006</t>
+  </si>
+  <si>
+    <t>0.0001,0.9994,0.0050,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0013,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0009,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.0006,0.0049,0.9967,0.0005</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9996,0.0002</t>
   </si>
   <si>
     <t>0.0001,0.0000,0.9999,0.0000</t>
   </si>
   <si>
-    <t>0.0019,0.0006,0.9959,0.0005</t>
-  </si>
-  <si>
-    <t>0.2428,0.0001,0.9073,0.0000</t>
-  </si>
-  <si>
-    <t>0.0222,0.0002,0.9813,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0002</t>
-  </si>
-  <si>
-    <t>0.6431,0.3112,0.0043,0.0004</t>
-  </si>
-  <si>
-    <t>0.7040,0.1874,0.0118,0.0007</t>
-  </si>
-  <si>
-    <t>0.0008,0.0026,0.9987,0.0056</t>
-  </si>
-  <si>
-    <t>0.0007,0.9960,0.0083,0.0002</t>
-  </si>
-  <si>
-    <t>0.9968,0.0019,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.7943,0.0323,0.0618,0.0030</t>
-  </si>
-  <si>
-    <t>0.8202,0.1742,0.0071,0.0001</t>
-  </si>
-  <si>
-    <t>0.0007,0.9984,0.0011,0.0001</t>
-  </si>
-  <si>
-    <t>0.0137,0.2800,0.4680,0.0057</t>
-  </si>
-  <si>
-    <t>0.0099,0.0020,0.9647,0.0165</t>
-  </si>
-  <si>
-    <t>0.0031,0.0052,0.9896,0.0010</t>
-  </si>
-  <si>
-    <t>0.0006,0.0001,0.9981,0.0014</t>
-  </si>
-  <si>
-    <t>0.0006,0.0144,0.9979,0.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.9973,0.0015,0.0002</t>
-  </si>
-  <si>
-    <t>0.0004,0.0003,0.9988,0.0005</t>
-  </si>
-  <si>
-    <t>0.0004,0.6122,0.0007,0.9904</t>
-  </si>
-  <si>
-    <t>0.0006,0.9978,0.0040,0.0004</t>
-  </si>
-  <si>
-    <t>0.0001,0.9985,0.0160,0.0005</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0003,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.0211,0.9942,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.0003,0.9997,0.0002</t>
+    <t>0.0001,0.0002,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0008,0.9988,0.0002</t>
+  </si>
+  <si>
+    <t>0.9962,0.0035,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9738,0.0068,0.0138,0.0003</t>
+  </si>
+  <si>
+    <t>0.0009,0.0042,0.9989,0.0018</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9980,0.0021,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9971,0.0023,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.9505,0.9539,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0019,0.9992,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0009,0.9994,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.9834,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.9997,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9401,0.0000,0.1632,0.0000</t>
+  </si>
+  <si>
+    <t>0.3200,0.0001,0.8389,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0013,0.9997,0.0005</t>
+  </si>
+  <si>
+    <t>0.0003,0.9608,0.8503,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9742,0.9345,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0523,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9991,0.9697,0.0000</t>
+  </si>
+  <si>
+    <t>0.0023,0.0000,0.0009,0.9983</t>
+  </si>
+  <si>
+    <t>0.0001,0.0005,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0008,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0019,0.0001,0.0015,0.9985</t>
+  </si>
+  <si>
+    <t>0.0003,0.0002,0.0004,0.9996</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.0001,0.9999</t>
+  </si>
+  <si>
+    <t>0.0002,0.9952,0.2300,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9928,0.9651,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.8802,0.9952,0.0000</t>
+  </si>
+  <si>
+    <t>0.0008,0.0327,0.9880,0.0014</t>
+  </si>
+  <si>
+    <t>0.0000,0.9899,0.9952,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.7623,0.9907,0.0000</t>
+  </si>
+  <si>
+    <t>0.9989,0.0008,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9988,0.0016,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9999,0.0002</t>
+  </si>
+  <si>
+    <t>0.0011,0.0048,0.9970,0.0006</t>
+  </si>
+  <si>
+    <t>0.9981,0.0000,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.9992,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9995,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9996,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.1265,0.9338,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.2479,0.0382,0.5386,0.0011</t>
+  </si>
+  <si>
+    <t>0.9632,0.0000,0.0731,0.0000</t>
+  </si>
+  <si>
+    <t>0.0559,0.0640,0.6851,0.0071</t>
+  </si>
+  <si>
+    <t>0.7505,0.1293,0.0073,0.0025</t>
+  </si>
+  <si>
+    <t>0.0017,0.0109,0.0047,0.9957</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0054,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0001,0.0080</t>
+  </si>
+  <si>
+    <t>0.0000,0.9992,0.9956,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9998,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.8235,0.0868,0.0198,0.0001</t>
+  </si>
+  <si>
+    <t>0.7328,0.3266,0.0012,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9984,0.0002,0.0009,0.0003</t>
+  </si>
+  <si>
+    <t>0.9990,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0003,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9983,0.0003,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9984,0.0003,0.0010,0.0001</t>
+  </si>
+  <si>
+    <t>0.0008,0.0595,0.9829,0.0015</t>
+  </si>
+  <si>
+    <t>0.0001,0.6001,0.9951,0.0000</t>
+  </si>
+  <si>
+    <t>0.0008,0.0028,0.9982,0.0001</t>
+  </si>
+  <si>
+    <t>0.0012,0.0008,0.9973,0.0002</t>
+  </si>
+  <si>
+    <t>0.9900,0.0004,0.0048,0.0001</t>
+  </si>
+  <si>
+    <t>0.5431,0.0007,0.4636,0.0005</t>
+  </si>
+  <si>
+    <t>0.0047,0.0004,0.9959,0.0003</t>
+  </si>
+  <si>
+    <t>0.9581,0.0010,0.0289,0.0007</t>
+  </si>
+  <si>
+    <t>0.4725,0.0000,0.0000,0.6976</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0005,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.0001,0.0000,0.9997</t>
+  </si>
+  <si>
+    <t>0.0000,0.9984,0.7648,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.1115,0.9078,0.0007,0.0012</t>
+  </si>
+  <si>
+    <t>0.9991,0.0002,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9250,0.1333,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.2283,0.0017,0.0043,0.8383</t>
+  </si>
+  <si>
+    <t>0.0002,0.0009,0.9989,0.0040</t>
+  </si>
+  <si>
+    <t>0.9875,0.0001,0.0046,0.0027</t>
+  </si>
+  <si>
+    <t>0.9964,0.0009,0.0007,0.0007</t>
+  </si>
+  <si>
+    <t>0.0231,0.9775,0.0005,0.0004</t>
+  </si>
+  <si>
+    <t>0.9484,0.0145,0.0180,0.0014</t>
+  </si>
+  <si>
+    <t>0.9984,0.0002,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.4481,0.4745,0.0072,0.0008</t>
+  </si>
+  <si>
+    <t>0.5399,0.0079,0.3508,0.0001</t>
+  </si>
+  <si>
+    <t>0.3248,0.6818,0.0034,0.0005</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9979,0.0007,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9875,0.0089,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.6166,0.5111,0.0011,0.0000</t>
+  </si>
+  <si>
+    <t>0.2332,0.8183,0.0009,0.0003</t>
+  </si>
+  <si>
+    <t>0.3521,0.0442,0.5579,0.0003</t>
+  </si>
+  <si>
+    <t>0.9874,0.0163,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9980,0.0016,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9993,0.0002,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9944,0.0038,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.0004,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.9873,0.0064,0.0027,0.0007</t>
   </si>
   <si>
     <t>0.0004,0.0001,0.9997,0.0000</t>
   </si>
   <si>
-    <t>0.0001,0.0001,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.0006,0.9987,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0005,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9956,0.0035,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.0012,0.0017,0.9990,0.0011</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0008,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9954,0.0054,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9800,0.9866,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0011,0.9995,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0136,0.9991,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9357,0.9989,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9997,0.0008</t>
-  </si>
-  <si>
-    <t>0.0001,0.9999,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9929,0.0002,0.0087,0.0000</t>
-  </si>
-  <si>
-    <t>0.5410,0.0003,0.5693,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.0004,0.9999,0.0017</t>
-  </si>
-  <si>
-    <t>0.0000,0.9912,0.9665,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9912,0.8869,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9993,0.6764,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9967,0.9322,0.0000</t>
-  </si>
-  <si>
-    <t>0.0072,0.0000,0.0048,0.9919</t>
-  </si>
-  <si>
-    <t>0.0001,0.0003,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0001,0.0005,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0004,0.0005,0.0024,0.9992</t>
-  </si>
-  <si>
-    <t>0.0013,0.0006,0.0009,0.9987</t>
-  </si>
-  <si>
-    <t>0.0004,0.0001,0.0003,0.9996</t>
-  </si>
-  <si>
-    <t>0.0001,0.9945,0.7244,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9863,0.9650,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9674,0.9790,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.5280,0.8639,0.0025</t>
-  </si>
-  <si>
-    <t>0.0000,0.9815,0.9985,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9974,0.9829,0.0000</t>
-  </si>
-  <si>
-    <t>0.9987,0.0007,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0003,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9986,0.0012,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9999,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9983,0.0004,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0002,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9999,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0014,0.0002,0.9983,0.0005</t>
-  </si>
-  <si>
-    <t>0.0006,0.0017,0.9986,0.0001</t>
-  </si>
-  <si>
-    <t>0.9852,0.0005,0.0067,0.0004</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.0010,0.9983,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.9995,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.5228,0.5570,0.0019,0.0003</t>
-  </si>
-  <si>
-    <t>0.2595,0.0109,0.6245,0.0010</t>
-  </si>
-  <si>
-    <t>0.9864,0.0008,0.0063,0.0001</t>
-  </si>
-  <si>
-    <t>0.1912,0.2556,0.1131,0.0021</t>
-  </si>
-  <si>
-    <t>0.1323,0.0071,0.7916,0.0046</t>
-  </si>
-  <si>
-    <t>0.0009,0.0245,0.0020,0.9962</t>
-  </si>
-  <si>
-    <t>0.0004,0.9991,0.0049,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9988,0.9950,0.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.9992,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.7345,0.2554,0.0055,0.0001</t>
-  </si>
-  <si>
-    <t>0.5597,0.5247,0.0013,0.0001</t>
+    <t>0.0062,0.0298,0.9831,0.0004</t>
+  </si>
+  <si>
+    <t>0.0006,0.0262,0.9961,0.0004</t>
+  </si>
+  <si>
+    <t>0.0001,0.0136,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0017,0.0000,0.9988,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9998,0.0002</t>
+  </si>
+  <si>
+    <t>0.0122,0.0010,0.9854,0.0003</t>
+  </si>
+  <si>
+    <t>0.0113,0.0001,0.9942,0.0000</t>
+  </si>
+  <si>
+    <t>0.0158,0.0061,0.9721,0.0010</t>
+  </si>
+  <si>
+    <t>0.0084,0.0014,0.9875,0.0004</t>
+  </si>
+  <si>
+    <t>0.0124,0.0157,0.9736,0.0006</t>
+  </si>
+  <si>
+    <t>0.5054,0.0062,0.4355,0.0002</t>
+  </si>
+  <si>
+    <t>0.9538,0.0026,0.0248,0.0014</t>
+  </si>
+  <si>
+    <t>0.0853,0.0038,0.8922,0.0024</t>
+  </si>
+  <si>
+    <t>0.0068,0.9932,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.0044,0.9962,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0203,0.9821,0.0004,0.0005</t>
+  </si>
+  <si>
+    <t>0.9848,0.0125,0.0022,0.0003</t>
+  </si>
+  <si>
+    <t>0.1078,0.9312,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.6181,0.3349,0.0011,0.0006</t>
+  </si>
+  <si>
+    <t>0.9962,0.0001,0.0025,0.0000</t>
+  </si>
+  <si>
+    <t>0.9724,0.0024,0.0088,0.0011</t>
+  </si>
+  <si>
+    <t>0.0168,0.0068,0.9776,0.0010</t>
+  </si>
+  <si>
+    <t>0.0095,0.0026,0.9838,0.0036</t>
+  </si>
+  <si>
+    <t>0.0002,0.0013,0.9993,0.0043</t>
+  </si>
+  <si>
+    <t>0.0004,0.0045,0.9986,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0030,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0117,0.0013,0.9827,0.0008</t>
+  </si>
+  <si>
+    <t>0.0008,0.0195,0.9949,0.0005</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0002,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9977,0.0027,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9976,0.0012,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0032,0.0143,0.9876,0.0018</t>
+  </si>
+  <si>
+    <t>0.9207,0.0004,0.0592,0.0031</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0005,0.9997,0.0008</t>
+  </si>
+  <si>
+    <t>0.0007,0.0088,0.9982,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0010,0.9991,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.0004,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0016,0.0010,0.9969,0.0001</t>
+  </si>
+  <si>
+    <t>0.0006,0.0027,0.9982,0.0004</t>
+  </si>
+  <si>
+    <t>0.9288,0.0016,0.0554,0.0003</t>
+  </si>
+  <si>
+    <t>0.5705,0.0004,0.4641,0.0011</t>
+  </si>
+  <si>
+    <t>0.9704,0.0002,0.0352,0.0002</t>
+  </si>
+  <si>
+    <t>0.9993,0.0002,0.0002,0.0000</t>
   </si>
   <si>
     <t>0.9996,0.0002,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9998,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9964,0.0010,0.0016,0.0003</t>
-  </si>
-  <si>
-    <t>0.0003,0.5468,0.9607,0.0010</t>
-  </si>
-  <si>
-    <t>0.0004,0.5093,0.9875,0.0000</t>
-  </si>
-  <si>
-    <t>0.0052,0.0034,0.9904,0.0003</t>
-  </si>
-  <si>
-    <t>0.0005,0.0005,0.9990,0.0000</t>
-  </si>
-  <si>
-    <t>0.9855,0.0002,0.0100,0.0002</t>
-  </si>
-  <si>
-    <t>0.0273,0.0010,0.9701,0.0015</t>
-  </si>
-  <si>
-    <t>0.0027,0.0002,0.9965,0.0008</t>
-  </si>
-  <si>
-    <t>0.3889,0.0011,0.6385,0.0006</t>
-  </si>
-  <si>
-    <t>0.0515,0.0001,0.0000,0.9887</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0007,0.0001,1.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.0000,0.0000,0.9998</t>
-  </si>
-  <si>
-    <t>0.0000,0.9970,0.9699,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0347,0.9719,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.9988,0.0002,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9157,0.1200,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.2699,0.0002,0.0010,0.8800</t>
-  </si>
-  <si>
-    <t>0.0009,0.0056,0.9978,0.0021</t>
-  </si>
-  <si>
-    <t>0.9822,0.0002,0.0069,0.0033</t>
-  </si>
-  <si>
-    <t>0.9952,0.0008,0.0024,0.0008</t>
-  </si>
-  <si>
-    <t>0.0078,0.9906,0.0012,0.0002</t>
-  </si>
-  <si>
-    <t>0.9932,0.0015,0.0018,0.0003</t>
-  </si>
-  <si>
-    <t>0.9991,0.0001,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.1648,0.8088,0.0042,0.0012</t>
-  </si>
-  <si>
-    <t>0.9868,0.0048,0.0036,0.0001</t>
-  </si>
-  <si>
-    <t>0.8320,0.0715,0.0163,0.0007</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9951,0.0022,0.0004,0.0004</t>
-  </si>
-  <si>
-    <t>0.9892,0.0080,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.3775,0.6483,0.0049,0.0001</t>
-  </si>
-  <si>
-    <t>0.5217,0.5965,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.9881,0.0071,0.0012,0.0011</t>
-  </si>
-  <si>
-    <t>0.9981,0.0016,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9984,0.0009,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9975,0.0015,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0003,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.9869,0.0034,0.0057,0.0008</t>
-  </si>
-  <si>
-    <t>0.0014,0.0001,0.9991,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.0240,0.9983,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.0001,0.9995,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0388,0.9971,0.0007</t>
-  </si>
-  <si>
-    <t>0.0014,0.0034,0.9985,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0001,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.9999,0.0004</t>
-  </si>
-  <si>
-    <t>0.0008,0.0006,0.9983,0.0001</t>
-  </si>
-  <si>
-    <t>0.0065,0.0034,0.9899,0.0004</t>
-  </si>
-  <si>
-    <t>0.0026,0.0025,0.9925,0.0019</t>
-  </si>
-  <si>
-    <t>0.3788,0.0957,0.1502,0.0003</t>
-  </si>
-  <si>
-    <t>0.0263,0.3548,0.4740,0.0003</t>
-  </si>
-  <si>
-    <t>0.0327,0.0005,0.9759,0.0001</t>
-  </si>
-  <si>
-    <t>0.8615,0.0027,0.1130,0.0009</t>
-  </si>
-  <si>
-    <t>0.0380,0.0014,0.9656,0.0009</t>
-  </si>
-  <si>
-    <t>0.0100,0.9883,0.0009,0.0003</t>
-  </si>
-  <si>
-    <t>0.0019,0.9975,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.1261,0.9089,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9298,0.1048,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.0298,0.9750,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9829,0.0080,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.9977,0.0002,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.9637,0.0068,0.0071,0.0010</t>
-  </si>
-  <si>
-    <t>0.1311,0.0036,0.8860,0.0006</t>
-  </si>
-  <si>
-    <t>0.0446,0.0049,0.9551,0.0015</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9998,0.0010</t>
-  </si>
-  <si>
-    <t>0.0005,0.0091,0.9971,0.0007</t>
-  </si>
-  <si>
-    <t>0.0008,0.0240,0.9960,0.0003</t>
-  </si>
-  <si>
-    <t>0.0364,0.0013,0.9514,0.0014</t>
-  </si>
-  <si>
-    <t>0.0001,0.0013,0.9992,0.0002</t>
-  </si>
-  <si>
-    <t>0.9969,0.0018,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9992,0.0007,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0003,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0002,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0004,0.9998,0.0003</t>
-  </si>
-  <si>
-    <t>0.0263,0.0043,0.9534,0.0130</t>
-  </si>
-  <si>
-    <t>0.9943,0.0014,0.0013,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0006,0.9994,0.0005</t>
-  </si>
-  <si>
-    <t>0.0001,0.0130,0.9993,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0013,0.0019,0.9965,0.0002</t>
-  </si>
-  <si>
-    <t>0.0019,0.0013,0.9963,0.0006</t>
-  </si>
-  <si>
-    <t>0.1855,0.0011,0.8011,0.0019</t>
-  </si>
-  <si>
-    <t>0.7748,0.0000,0.3874,0.0001</t>
-  </si>
-  <si>
-    <t>0.9975,0.0000,0.0019,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
     <t>0.9996,0.0003,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.0048,0.0025,0.9909,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.0022,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.0011,0.0089,0.9939,0.0015</t>
-  </si>
-  <si>
-    <t>0.0002,0.0008,0.9995,0.0001</t>
-  </si>
-  <si>
-    <t>0.0346,0.0011,0.9553,0.0015</t>
-  </si>
-  <si>
-    <t>0.0236,0.0056,0.9546,0.0025</t>
-  </si>
-  <si>
-    <t>0.0145,0.0008,0.9777,0.0013</t>
-  </si>
-  <si>
-    <t>0.9995,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0034,0.0000,0.9997</t>
-  </si>
-  <si>
-    <t>0.0073,0.0003,0.0003,0.9974</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.9810,0.0008,0.0008,0.0023</t>
+    <t>0.9995,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0007,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0062,0.0023,0.9893,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0024,0.9984,0.0002</t>
+  </si>
+  <si>
+    <t>0.0026,0.0213,0.9775,0.0023</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.0131,0.0061,0.9465,0.0123</t>
+  </si>
+  <si>
+    <t>0.0025,0.0021,0.9948,0.0013</t>
+  </si>
+  <si>
+    <t>0.0289,0.0016,0.9439,0.0028</t>
+  </si>
+  <si>
+    <t>0.9995,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0006,0.0003,0.0001,0.9997</t>
+  </si>
+  <si>
+    <t>0.0221,0.0000,0.0001,0.9957</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.9967,0.0002,0.0002,0.0002</t>
   </si>
 </sst>
 </file>
@@ -1860,7 +1863,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1874,7 +1877,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1888,7 +1891,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1899,10 +1902,10 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1916,7 +1919,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1930,7 +1933,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1944,7 +1947,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1958,7 +1961,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1972,7 +1975,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1986,7 +1989,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2000,7 +2003,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2014,7 +2017,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2028,7 +2031,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2042,7 +2045,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2056,7 +2059,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2070,7 +2073,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2084,7 +2087,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2098,7 +2101,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2112,7 +2115,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2126,7 +2129,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2140,7 +2143,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2154,7 +2157,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2168,7 +2171,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2182,7 +2185,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2196,7 +2199,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2210,7 +2213,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2224,7 +2227,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2238,7 +2241,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2252,7 +2255,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2263,10 +2266,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2277,10 +2280,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D32" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2294,7 +2297,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2308,7 +2311,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2322,7 +2325,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2336,7 +2339,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2350,7 +2353,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2364,7 +2367,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2375,10 +2378,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2392,7 +2395,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2406,7 +2409,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2420,7 +2423,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2434,7 +2437,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2448,7 +2451,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2462,7 +2465,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2473,10 +2476,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2490,7 +2493,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2504,7 +2507,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2518,7 +2521,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2532,7 +2535,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2546,7 +2549,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2560,7 +2563,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2574,7 +2577,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2588,7 +2591,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2602,7 +2605,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2616,7 +2619,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2630,7 +2633,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2644,7 +2647,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2658,7 +2661,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2672,7 +2675,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2686,7 +2689,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2700,7 +2703,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2714,7 +2717,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2728,7 +2731,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2742,7 +2745,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2756,7 +2759,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2770,7 +2773,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2784,7 +2787,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2798,7 +2801,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2812,7 +2815,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2826,7 +2829,7 @@
         <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2840,7 +2843,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2854,7 +2857,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2868,7 +2871,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2879,10 +2882,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2896,7 +2899,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2910,7 +2913,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2924,7 +2927,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2938,7 +2941,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2952,7 +2955,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2966,7 +2969,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2980,7 +2983,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2991,10 +2994,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D83" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3008,7 +3011,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3022,7 +3025,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3033,10 +3036,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3050,7 +3053,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3064,7 +3067,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3078,7 +3081,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3092,7 +3095,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3106,7 +3109,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3120,7 +3123,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>351</v>
+        <v>321</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3134,7 +3137,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3148,7 +3151,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>351</v>
+        <v>272</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3162,7 +3165,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>353</v>
+        <v>272</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3190,7 +3193,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3204,7 +3207,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3218,7 +3221,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3232,7 +3235,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3246,7 +3249,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3260,7 +3263,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>351</v>
+        <v>273</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3274,7 +3277,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>319</v>
+        <v>270</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3288,7 +3291,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>355</v>
+        <v>270</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3302,7 +3305,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3316,7 +3319,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3330,7 +3333,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3344,7 +3347,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3358,7 +3361,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>327</v>
+        <v>359</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3372,7 +3375,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3481,7 +3484,7 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D118" t="s">
         <v>367</v>
@@ -3495,7 +3498,7 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D119" t="s">
         <v>368</v>
@@ -3607,7 +3610,7 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D127" t="s">
         <v>376</v>
@@ -3624,7 +3627,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3652,7 +3655,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>378</v>
+        <v>275</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3666,7 +3669,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3680,7 +3683,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>270</v>
+        <v>379</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3733,7 +3736,7 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D136" t="s">
         <v>383</v>
@@ -3803,7 +3806,7 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D141" t="s">
         <v>388</v>
@@ -3831,7 +3834,7 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D143" t="s">
         <v>390</v>
@@ -3974,7 +3977,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>400</v>
+        <v>379</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3988,7 +3991,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4002,7 +4005,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4016,7 +4019,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4030,7 +4033,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4044,7 +4047,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4058,7 +4061,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4072,7 +4075,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4086,7 +4089,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4097,10 +4100,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D162" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4114,7 +4117,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4125,10 +4128,10 @@
         <v>259</v>
       </c>
       <c r="C164" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D164" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4142,7 +4145,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4156,7 +4159,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>380</v>
+        <v>321</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4170,7 +4173,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4184,7 +4187,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>412</v>
+        <v>275</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4198,7 +4201,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>319</v>
+        <v>377</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4212,7 +4215,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4226,7 +4229,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4240,7 +4243,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4254,7 +4257,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4265,10 +4268,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D174" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4282,7 +4285,7 @@
         <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4293,10 +4296,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4310,7 +4313,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4324,7 +4327,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4338,7 +4341,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4352,7 +4355,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4366,7 +4369,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4380,7 +4383,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4394,7 +4397,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4408,7 +4411,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4422,7 +4425,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>426</v>
+        <v>314</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4436,7 +4439,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4450,7 +4453,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4464,7 +4467,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4478,7 +4481,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4492,7 +4495,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4506,7 +4509,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4520,7 +4523,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4531,10 +4534,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4545,10 +4548,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4559,10 +4562,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4576,7 +4579,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4590,7 +4593,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4604,7 +4607,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4618,7 +4621,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4632,7 +4635,7 @@
         <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4646,7 +4649,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4660,7 +4663,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4674,7 +4677,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4688,7 +4691,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4702,7 +4705,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4716,7 +4719,7 @@
         <v>261</v>
       </c>
       <c r="D206" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4730,7 +4733,7 @@
         <v>261</v>
       </c>
       <c r="D207" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4744,7 +4747,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4758,7 +4761,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4772,7 +4775,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4786,7 +4789,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4800,7 +4803,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4814,7 +4817,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>353</v>
+        <v>377</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4828,7 +4831,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>400</v>
+        <v>451</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4842,7 +4845,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4856,7 +4859,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4870,7 +4873,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>456</v>
+        <v>272</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4884,7 +4887,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4898,7 +4901,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4926,7 +4929,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4940,7 +4943,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4954,7 +4957,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4968,7 +4971,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4982,7 +4985,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -4996,7 +4999,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5010,7 +5013,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5024,7 +5027,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5038,7 +5041,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5052,7 +5055,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5066,7 +5069,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5077,10 +5080,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5094,7 +5097,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5108,7 +5111,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5122,7 +5125,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>380</v>
+        <v>470</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5136,7 +5139,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>270</v>
+        <v>471</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5150,7 +5153,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>380</v>
+        <v>472</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5164,7 +5167,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5178,7 +5181,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>473</v>
+        <v>275</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5192,7 +5195,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5220,7 +5223,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>457</v>
+        <v>270</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5248,7 +5251,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>466</v>
+        <v>476</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5262,7 +5265,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5276,7 +5279,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5290,7 +5293,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5304,7 +5307,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5318,7 +5321,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5332,7 +5335,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5346,7 +5349,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5360,7 +5363,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5374,7 +5377,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5402,7 +5405,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5416,7 +5419,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
   </sheetData>
